--- a/public/samples/ja/sample1.xlsx
+++ b/public/samples/ja/sample1.xlsx
@@ -579,7 +579,7 @@
         <v>名前</v>
       </c>
       <c r="C2" s="3" t="str">
-        <v>性別♀</v>
+        <v>性別</v>
       </c>
       <c r="D2" s="3" t="str">
         <v>学習支援</v>
@@ -620,7 +620,7 @@
         <v>田中 綾香</v>
       </c>
       <c r="C3" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D3" s="3" t="str">
         <v>○</v>
@@ -651,6 +651,9 @@
       <c r="B4" s="3" t="str">
         <v>山本 武志</v>
       </c>
+      <c r="C4" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D4" s="3" t="str">
         <v>○</v>
       </c>
@@ -681,7 +684,7 @@
         <v>鈴木 美里</v>
       </c>
       <c r="C5" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E5" s="3" t="str">
         <v>○</v>
@@ -713,7 +716,7 @@
         <v>佐藤 可奈子</v>
       </c>
       <c r="C6" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G6" s="3">
         <v>3</v>
@@ -741,6 +744,9 @@
       <c r="B7" s="3" t="str">
         <v>伊藤 弘樹</v>
       </c>
+      <c r="C7" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="F7" s="3" t="str">
         <v>○</v>
       </c>
@@ -770,6 +776,9 @@
       <c r="B8" s="3" t="str">
         <v>小林 優太</v>
       </c>
+      <c r="C8" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G8" s="3">
         <v>2</v>
       </c>
@@ -799,6 +808,9 @@
       <c r="B9" s="3" t="str">
         <v>中村 芽衣</v>
       </c>
+      <c r="C9" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G9" s="3">
         <v>3</v>
       </c>
@@ -825,6 +837,9 @@
       <c r="B10" s="3" t="str">
         <v>加藤 信次</v>
       </c>
+      <c r="C10" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
@@ -852,7 +867,7 @@
         <v>斉藤 まどか</v>
       </c>
       <c r="C11" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F11" s="3" t="str">
         <v>○</v>
@@ -883,6 +898,9 @@
       <c r="B12" s="3" t="str">
         <v>三浦 太一</v>
       </c>
+      <c r="C12" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D12" s="3" t="str">
         <v>○</v>
       </c>
@@ -913,7 +931,7 @@
         <v>高橋 直美</v>
       </c>
       <c r="C13" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G13" s="3">
         <v>2</v>
@@ -941,6 +959,9 @@
       <c r="B14" s="3" t="str">
         <v>林 健治</v>
       </c>
+      <c r="C14" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G14" s="3">
         <v>2</v>
       </c>
@@ -967,6 +988,9 @@
       <c r="B15" s="3" t="str">
         <v>渡辺 明良</v>
       </c>
+      <c r="C15" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G15" s="3">
         <v>1</v>
       </c>
@@ -993,6 +1017,9 @@
       <c r="B16" s="3" t="str">
         <v>森田 愛</v>
       </c>
+      <c r="C16" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="E16" s="3" t="str">
         <v>○</v>
       </c>
@@ -1022,6 +1049,9 @@
       <c r="B17" s="3" t="str">
         <v>山田 孝史</v>
       </c>
+      <c r="C17" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G17" s="3">
         <v>3</v>
       </c>
@@ -1049,7 +1079,7 @@
         <v>井上 由貴</v>
       </c>
       <c r="C18" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -1078,7 +1108,7 @@
         <v>渋谷 理央</v>
       </c>
       <c r="C19" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="F19" s="3" t="str">
         <v>○</v>
@@ -1110,7 +1140,7 @@
         <v>佐々木 春香</v>
       </c>
       <c r="C20" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -1138,6 +1168,9 @@
       <c r="B21" s="3" t="str">
         <v>高木 和也</v>
       </c>
+      <c r="C21" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
@@ -1164,6 +1197,9 @@
       <c r="B22" s="3" t="str">
         <v>田村 充</v>
       </c>
+      <c r="C22" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D22" s="3" t="str">
         <v>○</v>
       </c>
@@ -1193,6 +1229,9 @@
       <c r="B23" s="3" t="str">
         <v>鈴木 亜莉斯</v>
       </c>
+      <c r="C23" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D23" s="3" t="str">
         <v>○</v>
       </c>
@@ -1225,6 +1264,9 @@
       <c r="B24" s="3" t="str">
         <v>田中 孝司</v>
       </c>
+      <c r="C24" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G24" s="3">
         <v>3</v>
       </c>
@@ -1251,6 +1293,9 @@
       <c r="B25" s="3" t="str">
         <v>山田 ジョン</v>
       </c>
+      <c r="C25" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G25" s="3">
         <v>1</v>
       </c>
@@ -1278,7 +1323,7 @@
         <v>佐藤 幸子</v>
       </c>
       <c r="C26" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G26" s="3">
         <v>3</v>
@@ -1307,7 +1352,7 @@
         <v>伊藤 花子</v>
       </c>
       <c r="C27" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D27" s="3" t="str">
         <v>○</v>
@@ -1338,6 +1383,9 @@
       <c r="B28" s="3" t="str">
         <v>小林 ジェイク</v>
       </c>
+      <c r="C28" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D28" s="3" t="str">
         <v>○</v>
       </c>
@@ -1368,7 +1416,7 @@
         <v>中村 未来</v>
       </c>
       <c r="C29" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
@@ -1396,6 +1444,9 @@
       <c r="B30" s="3" t="str">
         <v>加藤 琳</v>
       </c>
+      <c r="C30" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G30" s="3">
         <v>1</v>
       </c>
@@ -1423,7 +1474,7 @@
         <v>斉藤 恵里香</v>
       </c>
       <c r="C31" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D31" s="3" t="str">
         <v>○</v>
@@ -1454,6 +1505,9 @@
       <c r="B32" s="3" t="str">
         <v>三浦 太郎</v>
       </c>
+      <c r="C32" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D32" s="3" t="str">
         <v>○</v>
       </c>
@@ -1484,7 +1538,7 @@
         <v>高橋 絵麻</v>
       </c>
       <c r="C33" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G33" s="3">
         <v>3</v>
@@ -1513,7 +1567,7 @@
         <v>林 イヴ</v>
       </c>
       <c r="C34" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -1541,6 +1595,9 @@
       <c r="B35" s="3" t="str">
         <v>渡辺 怜</v>
       </c>
+      <c r="C35" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G35" s="3">
         <v>3</v>
       </c>
@@ -1568,7 +1625,7 @@
         <v>森田 雄希</v>
       </c>
       <c r="C36" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G36" s="3">
         <v>2</v>
@@ -1597,7 +1654,7 @@
         <v>山田 真理</v>
       </c>
       <c r="C37" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="E37" s="3" t="str">
         <v>○</v>
@@ -1629,7 +1686,7 @@
         <v>井上 翔</v>
       </c>
       <c r="C38" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G38" s="3">
         <v>1</v>
@@ -1658,7 +1715,7 @@
         <v>渋谷 有紗</v>
       </c>
       <c r="C39" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G39" s="3">
         <v>2</v>
@@ -1686,6 +1743,9 @@
       <c r="B40" s="3" t="str">
         <v>佐々木 賢</v>
       </c>
+      <c r="C40" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G40" s="3">
         <v>3</v>
       </c>
@@ -1712,6 +1772,9 @@
       <c r="B41" s="3" t="str">
         <v>高木 亜里愛</v>
       </c>
+      <c r="C41" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D41" s="3" t="str">
         <v>○</v>
       </c>
@@ -1741,6 +1804,9 @@
       <c r="B42" s="3" t="str">
         <v>田村 拓真</v>
       </c>
+      <c r="C42" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G42" s="3">
         <v>2</v>
       </c>
@@ -1768,7 +1834,7 @@
         <v>鈴木 美桜</v>
       </c>
       <c r="C43" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G43" s="3">
         <v>2</v>
@@ -1796,6 +1862,9 @@
       <c r="B44" s="3" t="str">
         <v>山本 健人</v>
       </c>
+      <c r="C44" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D44" s="3" t="str">
         <v>○</v>
       </c>
@@ -1829,7 +1898,7 @@
         <v>佐藤 静香</v>
       </c>
       <c r="C45" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G45" s="3">
         <v>2</v>
@@ -1857,6 +1926,9 @@
       <c r="B46" s="3" t="str">
         <v>伊藤 孝司</v>
       </c>
+      <c r="C46" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G46" s="3">
         <v>3</v>
       </c>
@@ -1884,7 +1956,7 @@
         <v>吉田 恵子</v>
       </c>
       <c r="C47" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G47" s="3">
         <v>2</v>
@@ -1912,6 +1984,9 @@
       <c r="B48" s="3" t="str">
         <v>坂本 拓海</v>
       </c>
+      <c r="C48" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G48" s="3">
         <v>1</v>
       </c>
@@ -1939,7 +2014,7 @@
         <v>川村 理香</v>
       </c>
       <c r="C49" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G49" s="3">
         <v>2</v>
@@ -1967,6 +2042,9 @@
       <c r="B50" s="3" t="str">
         <v>澤田 健治</v>
       </c>
+      <c r="C50" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G50" s="3">
         <v>1</v>
       </c>
@@ -1993,6 +2071,9 @@
       <c r="B51" s="3" t="str">
         <v>久保 桜</v>
       </c>
+      <c r="C51" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G51" s="3">
         <v>2</v>
       </c>
@@ -2019,6 +2100,9 @@
       <c r="B52" s="3" t="str">
         <v>石井 博士</v>
       </c>
+      <c r="C52" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D52" s="3" t="str">
         <v>○</v>
       </c>
@@ -2048,6 +2132,9 @@
       <c r="B53" s="3" t="str">
         <v>木村 ソフィア</v>
       </c>
+      <c r="C53" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D53" s="3" t="str">
         <v>○</v>
       </c>
@@ -2077,6 +2164,9 @@
       <c r="B54" s="3" t="str">
         <v>佐藤 拓郎</v>
       </c>
+      <c r="C54" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D54" s="3" t="str">
         <v>○</v>
       </c>
@@ -2107,7 +2197,7 @@
         <v>和田 理央</v>
       </c>
       <c r="C55" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G55" s="3">
         <v>3</v>
@@ -2136,7 +2226,7 @@
         <v>石川 光</v>
       </c>
       <c r="C56" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G56" s="3">
         <v>3</v>
@@ -2165,7 +2255,7 @@
         <v>境 泉</v>
       </c>
       <c r="C57" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G57" s="3">
         <v>2</v>
@@ -2194,7 +2284,7 @@
         <v>松田 慶</v>
       </c>
       <c r="C58" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G58" s="3">
         <v>3</v>
@@ -2222,6 +2312,9 @@
       <c r="B59" s="3" t="str">
         <v>中山 孝司</v>
       </c>
+      <c r="C59" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G59" s="3">
         <v>1</v>
       </c>
@@ -2249,7 +2342,7 @@
         <v>山口 小夜</v>
       </c>
       <c r="C60" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G60" s="3">
         <v>2</v>
@@ -2277,6 +2370,9 @@
       <c r="B61" s="3" t="str">
         <v>小川 優太</v>
       </c>
+      <c r="C61" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G61" s="3">
         <v>3</v>
       </c>
@@ -2304,7 +2400,7 @@
         <v>岡田 春樹</v>
       </c>
       <c r="C62" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G62" s="3">
         <v>3</v>
@@ -2333,7 +2429,7 @@
         <v>齋藤 香織</v>
       </c>
       <c r="C63" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G63" s="3">
         <v>3</v>
@@ -2361,6 +2457,9 @@
       <c r="B64" s="3" t="str">
         <v>中沢 慎也</v>
       </c>
+      <c r="C64" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G64" s="3">
         <v>3</v>
       </c>
@@ -2387,6 +2486,9 @@
       <c r="B65" s="3" t="str">
         <v>北村 菊男</v>
       </c>
+      <c r="C65" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G65" s="3">
         <v>1</v>
       </c>
@@ -2414,7 +2516,7 @@
         <v>櫻井 愛</v>
       </c>
       <c r="C66" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G66" s="3">
         <v>1</v>
@@ -2442,6 +2544,9 @@
       <c r="B67" s="3" t="str">
         <v>武田 卓司</v>
       </c>
+      <c r="C67" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G67" s="3">
         <v>2</v>
       </c>
@@ -2469,7 +2574,7 @@
         <v>田辺 玲奈</v>
       </c>
       <c r="C68" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G68" s="3">
         <v>2</v>
@@ -2497,6 +2602,9 @@
       <c r="B69" s="3" t="str">
         <v>石原 裕二</v>
       </c>
+      <c r="C69" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G69" s="3">
         <v>2</v>
       </c>
@@ -2524,7 +2632,7 @@
         <v>白石 真夜</v>
       </c>
       <c r="C70" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G70" s="3">
         <v>2</v>
@@ -2552,6 +2660,9 @@
       <c r="B71" s="3" t="str">
         <v>岩崎 孝</v>
       </c>
+      <c r="C71" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G71" s="3">
         <v>2</v>
       </c>
@@ -2579,7 +2690,7 @@
         <v>佐川 玲子</v>
       </c>
       <c r="C72" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D72" s="3" t="str">
         <v>○</v>
@@ -2610,6 +2721,9 @@
       <c r="B73" s="3" t="str">
         <v>中村 和也</v>
       </c>
+      <c r="C73" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G73" s="3">
         <v>1</v>
       </c>
@@ -2637,7 +2751,7 @@
         <v>浜田 春菜</v>
       </c>
       <c r="C74" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G74" s="3">
         <v>3</v>
@@ -2665,6 +2779,9 @@
       <c r="B75" s="3" t="str">
         <v>森山 圭太</v>
       </c>
+      <c r="C75" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="D75" s="3" t="str">
         <v>○</v>
       </c>
@@ -2695,7 +2812,7 @@
         <v>大野 美穂</v>
       </c>
       <c r="C76" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D76" s="3" t="str">
         <v>○</v>
@@ -2726,6 +2843,9 @@
       <c r="B77" s="3" t="str">
         <v>金子 亮</v>
       </c>
+      <c r="C77" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G77" s="3">
         <v>3</v>
       </c>
@@ -2753,7 +2873,7 @@
         <v>前田 真理菜</v>
       </c>
       <c r="C78" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D78" s="3" t="str">
         <v>○</v>
@@ -2785,7 +2905,7 @@
         <v>澤本 香織</v>
       </c>
       <c r="C79" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="D79" s="3" t="str">
         <v>○</v>
@@ -2816,6 +2936,9 @@
       <c r="B80" s="3" t="str">
         <v>塩谷 秀樹</v>
       </c>
+      <c r="C80" s="2" t="str">
+        <v>♂</v>
+      </c>
       <c r="G80" s="3">
         <v>3</v>
       </c>
@@ -2843,7 +2966,7 @@
         <v>井上 恵</v>
       </c>
       <c r="C81" s="3" t="str">
-        <v>〇</v>
+        <v>♀</v>
       </c>
       <c r="G81" s="3">
         <v>3</v>
@@ -2870,6 +2993,9 @@
       </c>
       <c r="B82" s="3" t="str">
         <v>清水 卓也</v>
+      </c>
+      <c r="C82" s="2" t="str">
+        <v>♂</v>
       </c>
       <c r="G82" s="3">
         <v>2</v>
